--- a/results/Int Task Remove ACC -1.0/Linea_fi_explain.xlsx
+++ b/results/Int Task Remove ACC -1.0/Linea_fi_explain.xlsx
@@ -1157,7 +1157,7 @@
         <v>0.005872884982739624</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03036821903365029</v>
+        <v>0.03037742486052871</v>
       </c>
       <c r="F3" t="n">
         <v>0.002184021847673482</v>
@@ -1166,28 +1166,28 @@
         <v>0.02170738218569015</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.001518232208034216</v>
+        <v>-0.001515277998285324</v>
       </c>
       <c r="I3" t="n">
-        <v>9.704229897145589e-05</v>
+        <v>9.406787898335379e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04462888530016795</v>
+        <v>0.04463495266929949</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02370122144811008</v>
+        <v>0.02370123192096927</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02370123192096927</v>
+        <v>0.02369531213395195</v>
       </c>
       <c r="M3" t="n">
         <v>0.01620193060290426</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04007005449555578</v>
+        <v>0.04007008167121733</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02040457414513764</v>
+        <v>0.02040442844032075</v>
       </c>
       <c r="P3" t="n">
         <v>0.00727366524777433</v>
@@ -1196,7 +1196,7 @@
         <v>0.01600343528415791</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01558995895677107</v>
+        <v>0.01558996592219341</v>
       </c>
       <c r="S3" t="n">
         <v>0.2945550448381226</v>
@@ -1208,7 +1208,7 @@
         <v>0.1195994144672543</v>
       </c>
       <c r="V3" t="n">
-        <v>9.702208873224594e-05</v>
+        <v>9.999650872034803e-05</v>
       </c>
       <c r="W3" t="n">
         <v>0.009002547139726124</v>
@@ -1223,7 +1223,7 @@
         <v>0.002661589083606499</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.03470825559115872</v>
+        <v>0.03470530660855772</v>
       </c>
       <c r="AB3" t="n">
         <v>0.001387737771559038</v>
@@ -1238,7 +1238,7 @@
         <v>0.219134857984074</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.08052698942756728</v>
+        <v>0.08052404218324075</v>
       </c>
       <c r="AG3" t="n">
         <v>0.08839249730421042</v>
@@ -1298,13 +1298,13 @@
         <v>0.0005320627135546617</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.01125344272624021</v>
+        <v>0.01125657654009167</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.006668047484373138</v>
+        <v>0.00666491367052168</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.006481908720889201</v>
+        <v>0.006484855965215755</v>
       </c>
       <c r="BC3" t="n">
         <v>-9.507847258011238e-06</v>
@@ -1319,7 +1319,7 @@
         <v>0.01421942358017777</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.004759592890526729</v>
+        <v>0.004762540134853284</v>
       </c>
       <c r="BH3" t="n">
         <v>0.0003456636822469416</v>
@@ -1367,7 +1367,7 @@
         <v>0.004557046064061585</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.008279933859219038</v>
+        <v>0.008282814873336005</v>
       </c>
       <c r="BX3" t="n">
         <v>-9.995999787123068e-05</v>
@@ -1385,7 +1385,7 @@
         <v>0.0008728987040084535</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.002030661982592071</v>
+        <v>0.002033623315349592</v>
       </c>
       <c r="CD3" t="n">
         <v>-0.0005948769398728627</v>
@@ -1406,7 +1406,7 @@
         <v>0.02972716091720777</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.008282814873336005</v>
+        <v>0.008279933859219038</v>
       </c>
       <c r="CK3" t="n">
         <v>0.007945659719451064</v>
@@ -1428,7 +1428,7 @@
         <v>0.01145012447400461</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03269553304985888</v>
+        <v>0.03270561724658556</v>
       </c>
       <c r="F4" t="n">
         <v>0.002920908574377343</v>
@@ -1437,28 +1437,28 @@
         <v>0.05468928294964336</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002932396248453816</v>
+        <v>0.002935629981215447</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001073030794171756</v>
+        <v>0.001070711668480681</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04428033735762881</v>
+        <v>0.04428297753759203</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01292095436028379</v>
+        <v>0.01291511426569985</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01291511426569985</v>
+        <v>0.0129211726324667</v>
       </c>
       <c r="M4" t="n">
         <v>0.03239192947161385</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04062795411781884</v>
+        <v>0.04063808109722671</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02975173678311191</v>
+        <v>0.02974371847460855</v>
       </c>
       <c r="P4" t="n">
         <v>0.01821371798657882</v>
@@ -1467,7 +1467,7 @@
         <v>0.02031017484773797</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01792438286811251</v>
+        <v>0.01792355908764708</v>
       </c>
       <c r="S4" t="n">
         <v>0.1032683491624796</v>
@@ -1479,7 +1479,7 @@
         <v>0.05451432125979587</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001070010979954793</v>
+        <v>0.001072322516150263</v>
       </c>
       <c r="W4" t="n">
         <v>0.02960615851271703</v>
@@ -1494,7 +1494,7 @@
         <v>0.01305070478122668</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03088476664660157</v>
+        <v>0.03088892562141527</v>
       </c>
       <c r="AB4" t="n">
         <v>0.002761503144583464</v>
@@ -1509,7 +1509,7 @@
         <v>0.1512933346162925</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1102644536620767</v>
+        <v>0.1102713846663821</v>
       </c>
       <c r="AG4" t="n">
         <v>0.04074889328102505</v>
@@ -1569,13 +1569,13 @@
         <v>0.02021877752644144</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.02811479475603972</v>
+        <v>0.02812195219494185</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.008711996682953943</v>
+        <v>0.008704581431167679</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.0147795718627242</v>
+        <v>0.01477808628566346</v>
       </c>
       <c r="BC4" t="n">
         <v>0.0006496816510989949</v>
@@ -1590,7 +1590,7 @@
         <v>0.02479461278151418</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.02423814092343936</v>
+        <v>0.02423454084635035</v>
       </c>
       <c r="BH4" t="n">
         <v>0.000935505780414492</v>
@@ -1638,7 +1638,7 @@
         <v>0.01937947570181254</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0261320507024158</v>
+        <v>0.02613627851621273</v>
       </c>
       <c r="BX4" t="n">
         <v>0.000181440443438089</v>
@@ -1656,7 +1656,7 @@
         <v>0.002169735804199412</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.01252958060285305</v>
+        <v>0.01252265553119706</v>
       </c>
       <c r="CD4" t="n">
         <v>0.004499814999036689</v>
@@ -1677,7 +1677,7 @@
         <v>0.03421238728413903</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.02613627851621273</v>
+        <v>0.0261320507024158</v>
       </c>
       <c r="CK4" t="n">
         <v>0.007317152099463472</v>
@@ -1717,10 +1717,10 @@
         <v>-0.01060513447432767</v>
       </c>
       <c r="K5" t="n">
+        <v>-0.003728913879846107</v>
+      </c>
+      <c r="L5" t="n">
         <v>-0.00375850843444806</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-0.003728913879846107</v>
       </c>
       <c r="M5" t="n">
         <v>-0.03057722308892354</v>
@@ -1780,7 +1780,7 @@
         <v>-0.1294724432655467</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.1528440907751252</v>
+        <v>-0.1528735632183908</v>
       </c>
       <c r="AG5" t="n">
         <v>0.01709401709401711</v>
@@ -1861,7 +1861,7 @@
         <v>-0.03180076628352486</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.02189802534630115</v>
+        <v>-0.0218685529030356</v>
       </c>
       <c r="BH5" t="n">
         <v>-0.0004735128736312433</v>
@@ -1927,7 +1927,7 @@
         <v>-0.001827291482463866</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.02452107279693483</v>
+        <v>-0.02449160035366928</v>
       </c>
       <c r="CD5" t="n">
         <v>-0.007644259369423001</v>
@@ -1985,10 +1985,10 @@
         <v>-0.0003933375892087698</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0150705706117513</v>
+        <v>0.01509267494420046</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01603419184060596</v>
+        <v>0.01602681938410345</v>
       </c>
       <c r="L6" t="n">
         <v>0.01602681938410345</v>
@@ -1997,7 +1997,7 @@
         <v>-0.003645962159384408</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01870371271668332</v>
+        <v>0.01868160838423417</v>
       </c>
       <c r="O6" t="n">
         <v>0.003122044731798476</v>
@@ -2009,7 +2009,7 @@
         <v>0.005242907033318573</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002751178571226448</v>
+        <v>0.002765967033526753</v>
       </c>
       <c r="S6" t="n">
         <v>0.2532194299970584</v>
@@ -2117,7 +2117,7 @@
         <v>0.0001794071762870275</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.0009657570363394124</v>
+        <v>-0.0009583889255230265</v>
       </c>
       <c r="BC6" t="n">
         <v>-0.0004067618652026733</v>
@@ -2241,7 +2241,7 @@
         <v>0.006716190707604358</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0181635069283667</v>
+        <v>0.01814873587962224</v>
       </c>
       <c r="F7" t="n">
         <v>0.001372902557349798</v>
@@ -2262,7 +2262,7 @@
         <v>0.02533043389710127</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02533043389710127</v>
+        <v>0.0253156322393156</v>
       </c>
       <c r="M7" t="n">
         <v>0.01463502598476664</v>
@@ -2512,7 +2512,7 @@
         <v>0.009667835795490395</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04048926962965924</v>
+        <v>0.04051147211633774</v>
       </c>
       <c r="F8" t="n">
         <v>0.00441173768307066</v>
@@ -2524,7 +2524,7 @@
         <v>0.0003655845657210138</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0007189617003364734</v>
+        <v>0.0006966535504257077</v>
       </c>
       <c r="J8" t="n">
         <v>0.07773980348720409</v>
@@ -2542,7 +2542,7 @@
         <v>0.04746392079923327</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02283809540458538</v>
+        <v>0.02286040355449614</v>
       </c>
       <c r="P8" t="n">
         <v>0.01693098670221116</v>
@@ -2563,7 +2563,7 @@
         <v>0.1507046894235935</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0006966535504257077</v>
+        <v>0.0007189617003364734</v>
       </c>
       <c r="W8" t="n">
         <v>0.03109551075958515</v>
@@ -2740,7 +2740,7 @@
         <v>0.001442111896370884</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.003060024816771137</v>
+        <v>0.003074932137789066</v>
       </c>
       <c r="CD8" t="n">
         <v>0.0003137230549890846</v>
@@ -2810,10 +2810,10 @@
         <v>0.0667256115531978</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1413741820345033</v>
+        <v>0.1414039262343843</v>
       </c>
       <c r="O9" t="n">
-        <v>0.09422776911076444</v>
+        <v>0.09419656786271453</v>
       </c>
       <c r="P9" t="n">
         <v>0.04489859594383776</v>
@@ -2924,10 +2924,10 @@
         <v>0.02829833907865874</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.06903791914760264</v>
+        <v>0.06906925728611722</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.02522720150423065</v>
+        <v>0.02519586336571609</v>
       </c>
       <c r="BB9" t="n">
         <v>0.03660294578502038</v>
@@ -2993,7 +2993,7 @@
         <v>0.04026950799122533</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.04278305963699228</v>
+        <v>0.04281186977816197</v>
       </c>
       <c r="BX9" t="n">
         <v>5.89448865311093e-05</v>
@@ -3032,7 +3032,7 @@
         <v>0.0759369422962522</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.04281186977816197</v>
+        <v>0.04278305963699228</v>
       </c>
       <c r="CK9" t="n">
         <v>0.02061273051754904</v>
